--- a/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$in）.xlsx
+++ b/internal_doc/05.测试设计/story/操作符/matches/Story-mathes测试用例（$in）.xlsx
@@ -83,24 +83,20 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、find{&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，$in指定多个值，且为不同类型的值
+    <t>1、find({&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，目标字段覆盖所有数据类型，取值个数覆盖：1个、多个
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，$in指定值为空，如{$in:[]}
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，目标字段为索引字段，且目标字段需要覆盖所有数据类型，取值个数覆盖：1个、多个
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，目标字段覆盖所有数据类型，取值个数覆盖：1个、多个
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$in指定多个值，且为不同类型的值
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、find{&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}}查询，目标字段为索引字段，且目标字段需要覆盖所有数据类型，取值个数覆盖：1个、多个
+  </si>
+  <si>
+    <t>1、find({&lt;字段名&gt;:{$in:[&lt;值1&gt;,&lt;值2&gt;,...&lt;值N&gt;]}})查询，$in指定值为空，如{$in:[]}
 2、检查查询结果正确性</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -631,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -657,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
@@ -684,7 +680,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
@@ -710,7 +706,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>15</v>
